--- a/data/trans_orig/RUIDO_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13796</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27855</t>
+          <t>27647</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>13032</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1776</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>17594</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16346</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23567</t>
+          <t>23792</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34931</t>
+          <t>35059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43047</t>
+          <t>42102</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111677</t>
+          <t>112469</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38440</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60592</t>
+          <t>59701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88791</t>
+          <t>89504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173909</t>
+          <t>178783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>48,49%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33379</t>
+          <t>33974</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74261</t>
+          <t>74429</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67263</t>
+          <t>68194</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92988</t>
+          <t>92783</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>109652</t>
+          <t>104965</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>158085</t>
+          <t>157877</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>28520</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23420</t>
+          <t>23166</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41723</t>
+          <t>41371</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38474</t>
+          <t>37443</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65853</t>
+          <t>64717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>12393</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30062</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25536</t>
+          <t>25206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27244</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50224</t>
+          <t>51018</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9437</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16768</t>
+          <t>16407</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16339</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22844</t>
+          <t>23709</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>20887</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32528</t>
+          <t>32292</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30938</t>
+          <t>31053</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45192</t>
+          <t>45439</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55064</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74403</t>
+          <t>73881</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>61,72%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16817</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>13391</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26438</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27724</t>
+          <t>27585</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29798</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52922</t>
+          <t>53566</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>55791</t>
+          <t>55080</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>140724</t>
+          <t>136617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>57236</t>
+          <t>58345</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>83368</t>
+          <t>83941</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120387</t>
+          <t>123170</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>211835</t>
+          <t>216486</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,99%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>64426</t>
+          <t>59231</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>109077</t>
+          <t>109268</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>109333</t>
+          <t>107996</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>140198</t>
+          <t>138537</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>183474</t>
+          <t>176866</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>240205</t>
+          <t>236771</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20217</t>
+          <t>21392</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41780</t>
+          <t>42580</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31987</t>
+          <t>33090</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>56497</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60701</t>
+          <t>58678</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90715</t>
+          <t>91213</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21136</t>
+          <t>22194</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42236</t>
+          <t>43342</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>40229</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>48499</t>
+          <t>48449</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>75975</t>
+          <t>74868</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4003</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>916</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7776</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10294</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6480</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15159</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>39,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>57,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7508</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3383</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14167</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>31,1%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19268</t>
+          <t>14903</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27647</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4708</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10174</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>38,73%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2824</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13032</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>28,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>53,98%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4244</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9025</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>34,35%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5015</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4802</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4212</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1478</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8109</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,61%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6142</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10671</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>23,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40,62%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4628</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9214</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,17%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17594</t>
+          <t>16840</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>26270</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>26270</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>26270</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>24143</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>24143</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>24143</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>52983</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>52983</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52983</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13896</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8905</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22059</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9324</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4514</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16098</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15493</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23792</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16761</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35059</t>
+          <t>33984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43656</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34423</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53509</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>30,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>65918</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>42102</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>112469</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>37,42%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>63,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48623</t>
+          <t>39287</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>30625</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59701</t>
+          <t>50003</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>114541</t>
+          <t>82943</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89504</t>
+          <t>70168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178783</t>
+          <t>98574</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>72936</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>61316</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>83895</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>40,91%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>47,06%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>59134</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>33974</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>74429</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>33,57%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,29%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>42,25%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>79705</t>
+          <t>58872</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>68194</t>
+          <t>49635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92783</t>
+          <t>68868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>138839</t>
+          <t>131808</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>104965</t>
+          <t>116452</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>157877</t>
+          <t>147417</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31213</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22844</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>42631</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,91%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19929</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11436</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28520</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,19%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31425</t>
+          <t>20231</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23166</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>27586</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>51353</t>
+          <t>51444</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37443</t>
+          <t>40141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64717</t>
+          <t>63912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16563</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10990</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>24976</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14,01%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>21848</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12393</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30558</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12,4%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>22221</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25206</t>
+          <t>30832</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>39183</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28816</t>
+          <t>29302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51018</t>
+          <t>49813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>178264</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>178264</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>178264</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>176153</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>176153</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>176153</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>192580</t>
+          <t>150057</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>192580</t>
+          <t>150057</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>192580</t>
+          <t>150057</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>368733</t>
+          <t>328322</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>368733</t>
+          <t>328322</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>368733</t>
+          <t>328322</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4685</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10341</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17,02%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5208</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2267</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9437</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>5885</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>17011</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6954</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3630</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>12283</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>11,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>6658</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3595</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>11875</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23709</t>
+          <t>19799</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>36630</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>29349</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>43011</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>60,28%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>48,3%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>70,78%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>26230</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>20887</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>32292</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>48,36%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>38,51%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>59,54%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>38738</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31053</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45439</t>
+          <t>31729</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>64969</t>
+          <t>62585</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>52611</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73881</t>
+          <t>71246</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7976</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3918</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13384</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>13,13%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,03%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>10326</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>6042</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>15842</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>19,04%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>29,21%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13391</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>26305</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4522</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5814</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2989</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10810</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>19,93%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>16985</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60767</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60767</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60767</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>54236</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>54236</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>54236</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>65457</t>
+          <t>53853</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65457</t>
+          <t>53853</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65457</t>
+          <t>53853</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>119694</t>
+          <t>114620</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>119694</t>
+          <t>114620</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>119694</t>
+          <t>114620</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>19463</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>13761</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>18535</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>10919</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>27585</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>13193</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30333</t>
+          <t>27935</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>40020</t>
+          <t>38688</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29753</t>
+          <t>28539</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53566</t>
+          <t>50895</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>60904</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>49828</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>74161</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>22,96%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>18,78%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>27,95%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>80084</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>55080</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>136617</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>31,46%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>21,64%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>53,67%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>69497</t>
+          <t>49985</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>40012</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>83941</t>
+          <t>61658</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>149581</t>
+          <t>110889</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>123170</t>
+          <t>96135</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>216486</t>
+          <t>128529</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>114274</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>101455</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>129627</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>43,07%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>38,24%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>48,86%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>92135</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>59231</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>109268</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>36,2%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>23,27%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>42,93%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>123418</t>
+          <t>89354</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>107996</t>
+          <t>76708</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>138537</t>
+          <t>100220</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>215553</t>
+          <t>203628</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>176866</t>
+          <t>185001</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>236771</t>
+          <t>220512</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>45,12%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>43433</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>33970</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>56378</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>21,25%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>31489</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>21392</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>42580</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>12,37%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>16,73%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>43201</t>
+          <t>31848</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>24429</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56497</t>
+          <t>41014</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>74690</t>
+          <t>75281</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58678</t>
+          <t>62392</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91213</t>
+          <t>89651</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>27227</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>18777</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>37628</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>10,26%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>14,18%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>32290</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>22194</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>43342</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>17,03%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>29276</t>
+          <t>33018</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>25248</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40229</t>
+          <t>42836</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>61565</t>
+          <t>60245</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>48449</t>
+          <t>48939</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>74868</t>
+          <t>74056</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>265302</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>265302</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>265302</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>254533</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>254533</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>254533</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>223429</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>223429</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>223429</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>541410</t>
+          <t>488730</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>541410</t>
+          <t>488730</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>541410</t>
+          <t>488730</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
